--- a/metadata/OtherViruses_known.xlsx
+++ b/metadata/OtherViruses_known.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexikeene/Documents/Research/papers/github_copy/Old_Collections_Figures/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C463169-3452-1F44-B200-F63C8580C425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFCF018-83AE-CC4C-B7D3-090F661A3257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31260" yWindow="1160" windowWidth="34640" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="10000" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OtherViruses_known" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="186">
   <si>
     <t>known</t>
   </si>
@@ -280,9 +280,6 @@
     <t>Novel</t>
   </si>
   <si>
-    <t>Unkown Drosophilidae</t>
-  </si>
-  <si>
     <t>Drosophila-associated sobemo-like virus</t>
   </si>
   <si>
@@ -575,6 +572,24 @@
   </si>
   <si>
     <t>control</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>cDNA_Neg</t>
+  </si>
+  <si>
+    <t>NegCtrl_NewPrep</t>
+  </si>
+  <si>
+    <t>Water_NegCtrl</t>
+  </si>
+  <si>
+    <t>D. putrida</t>
   </si>
 </sst>
 </file>
@@ -1435,9 +1450,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="31.1640625" customWidth="1"/>
     <col min="7" max="7" width="29.1640625" bestFit="1" customWidth="1"/>
@@ -1488,10 +1504,10 @@
         <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -1538,7 +1554,7 @@
         <v>18</v>
       </c>
       <c r="O2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -1579,13 +1595,13 @@
         <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -1614,25 +1630,25 @@
         <v>100</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J4" t="s">
         <v>24</v>
       </c>
       <c r="K4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L4" t="s">
         <v>23</v>
       </c>
       <c r="M4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
@@ -1661,25 +1677,25 @@
         <v>100</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J5" t="s">
         <v>26</v>
       </c>
       <c r="K5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L5" t="s">
         <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -1723,10 +1739,10 @@
         <v>31</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -1740,7 +1756,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
@@ -1773,7 +1789,7 @@
         <v>18</v>
       </c>
       <c r="O7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -1787,7 +1803,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
@@ -1820,7 +1836,7 @@
         <v>18</v>
       </c>
       <c r="O8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -1834,7 +1850,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
         <v>32</v>
@@ -1855,19 +1871,19 @@
         <v>33</v>
       </c>
       <c r="K9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L9" t="s">
         <v>23</v>
       </c>
       <c r="M9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -1881,7 +1897,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
         <v>32</v>
@@ -1908,13 +1924,13 @@
         <v>23</v>
       </c>
       <c r="M10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -1928,7 +1944,7 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
         <v>32</v>
@@ -1949,19 +1965,19 @@
         <v>26</v>
       </c>
       <c r="K11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L11" t="s">
         <v>23</v>
       </c>
       <c r="M11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -2008,7 +2024,7 @@
         <v>18</v>
       </c>
       <c r="O12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -2049,13 +2065,13 @@
         <v>23</v>
       </c>
       <c r="M13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -2090,19 +2106,19 @@
         <v>26</v>
       </c>
       <c r="K14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L14" t="s">
         <v>23</v>
       </c>
       <c r="M14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -2137,19 +2153,19 @@
         <v>50</v>
       </c>
       <c r="K15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L15" t="s">
         <v>23</v>
       </c>
       <c r="M15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
@@ -2196,7 +2212,7 @@
         <v>18</v>
       </c>
       <c r="O16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
@@ -2240,10 +2256,10 @@
         <v>31</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
@@ -2278,19 +2294,19 @@
         <v>24</v>
       </c>
       <c r="K18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L18" t="s">
         <v>23</v>
       </c>
       <c r="M18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
@@ -2331,13 +2347,13 @@
         <v>23</v>
       </c>
       <c r="M19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
@@ -2351,7 +2367,7 @@
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
         <v>57</v>
@@ -2384,7 +2400,7 @@
         <v>18</v>
       </c>
       <c r="O20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
@@ -2398,7 +2414,7 @@
         <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s">
         <v>57</v>
@@ -2431,7 +2447,7 @@
         <v>18</v>
       </c>
       <c r="O21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
@@ -2445,7 +2461,7 @@
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E22" t="s">
         <v>59</v>
@@ -2466,19 +2482,19 @@
         <v>24</v>
       </c>
       <c r="K22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L22" t="s">
         <v>23</v>
       </c>
       <c r="M22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
@@ -2492,7 +2508,7 @@
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E23" t="s">
         <v>59</v>
@@ -2522,10 +2538,10 @@
         <v>31</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
@@ -2539,7 +2555,7 @@
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E24" t="s">
         <v>59</v>
@@ -2554,25 +2570,25 @@
         <v>100</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J24" t="s">
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L24" t="s">
         <v>23</v>
       </c>
       <c r="M24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
@@ -2586,7 +2602,7 @@
         <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
         <v>59</v>
@@ -2613,13 +2629,13 @@
         <v>23</v>
       </c>
       <c r="M25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
@@ -2633,7 +2649,7 @@
         <v>58</v>
       </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
         <v>66</v>
@@ -2660,13 +2676,13 @@
         <v>19</v>
       </c>
       <c r="M26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
@@ -2680,7 +2696,7 @@
         <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s">
         <v>66</v>
@@ -2710,10 +2726,10 @@
         <v>38</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
@@ -2727,7 +2743,7 @@
         <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
         <v>66</v>
@@ -2748,19 +2764,19 @@
         <v>26</v>
       </c>
       <c r="K28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L28" t="s">
         <v>23</v>
       </c>
       <c r="M28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
@@ -2774,7 +2790,7 @@
         <v>58</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E29" t="s">
         <v>66</v>
@@ -2807,7 +2823,7 @@
         <v>18</v>
       </c>
       <c r="O29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
@@ -2821,7 +2837,7 @@
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s">
         <v>72</v>
@@ -2851,10 +2867,10 @@
         <v>75</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
@@ -2868,7 +2884,7 @@
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
         <v>72</v>
@@ -2889,7 +2905,7 @@
         <v>76</v>
       </c>
       <c r="K31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L31" t="s">
         <v>19</v>
@@ -2901,7 +2917,7 @@
         <v>18</v>
       </c>
       <c r="O31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
@@ -2915,7 +2931,7 @@
         <v>58</v>
       </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s">
         <v>66</v>
@@ -2936,19 +2952,19 @@
         <v>26</v>
       </c>
       <c r="K32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s">
         <v>23</v>
       </c>
       <c r="M32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O32" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
@@ -2959,43 +2975,43 @@
         <v>2003</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="D33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E33" t="s">
         <v>59</v>
       </c>
       <c r="F33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" t="s">
         <v>83</v>
-      </c>
-      <c r="G33" t="s">
-        <v>84</v>
       </c>
       <c r="H33">
         <v>100</v>
       </c>
       <c r="I33" t="s">
+        <v>84</v>
+      </c>
+      <c r="J33" t="s">
         <v>85</v>
       </c>
-      <c r="J33" t="s">
-        <v>86</v>
-      </c>
       <c r="K33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s">
         <v>23</v>
       </c>
       <c r="M33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N33" t="s">
         <v>18</v>
       </c>
       <c r="O33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.2">
@@ -3009,40 +3025,40 @@
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E34" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34" t="s">
         <v>88</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>89</v>
-      </c>
-      <c r="G34" t="s">
-        <v>90</v>
       </c>
       <c r="H34">
         <v>100</v>
       </c>
       <c r="I34" t="s">
+        <v>90</v>
+      </c>
+      <c r="J34" t="s">
         <v>91</v>
       </c>
-      <c r="J34" t="s">
-        <v>92</v>
-      </c>
       <c r="K34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s">
         <v>23</v>
       </c>
       <c r="M34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N34" t="s">
         <v>18</v>
       </c>
       <c r="O34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
@@ -3056,13 +3072,13 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E35" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G35" t="s">
         <v>18</v>
@@ -3071,10 +3087,10 @@
         <v>100</v>
       </c>
       <c r="I35" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K35">
         <v>99</v>
@@ -3083,13 +3099,13 @@
         <v>23</v>
       </c>
       <c r="M35" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N35" t="s">
         <v>18</v>
       </c>
       <c r="O35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
@@ -3103,10 +3119,10 @@
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
@@ -3118,25 +3134,25 @@
         <v>99.5</v>
       </c>
       <c r="I36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J36" t="s">
         <v>26</v>
       </c>
       <c r="K36" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L36" t="s">
         <v>23</v>
       </c>
       <c r="M36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N36" t="s">
         <v>18</v>
       </c>
       <c r="O36" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
@@ -3150,10 +3166,10 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F37" t="s">
         <v>36</v>
@@ -3183,7 +3199,7 @@
         <v>18</v>
       </c>
       <c r="O37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
@@ -3197,10 +3213,10 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E38" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F38" t="s">
         <v>67</v>
@@ -3224,13 +3240,13 @@
         <v>23</v>
       </c>
       <c r="M38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N38" t="s">
         <v>18</v>
       </c>
       <c r="O38" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
@@ -3244,13 +3260,13 @@
         <v>14</v>
       </c>
       <c r="D39" t="s">
+        <v>162</v>
+      </c>
+      <c r="E39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F39" t="s">
         <v>163</v>
-      </c>
-      <c r="E39" t="s">
-        <v>161</v>
-      </c>
-      <c r="F39" t="s">
-        <v>164</v>
       </c>
       <c r="G39" t="s">
         <v>18</v>
@@ -3259,10 +3275,10 @@
         <v>100</v>
       </c>
       <c r="I39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J39" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K39">
         <v>98.9</v>
@@ -3271,13 +3287,13 @@
         <v>23</v>
       </c>
       <c r="M39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N39" t="s">
         <v>18</v>
       </c>
       <c r="O39" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
@@ -3291,10 +3307,10 @@
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
@@ -3306,25 +3322,25 @@
         <v>99.1</v>
       </c>
       <c r="I40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J40" t="s">
         <v>26</v>
       </c>
       <c r="K40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L40" t="s">
         <v>23</v>
       </c>
       <c r="M40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N40" t="s">
         <v>18</v>
       </c>
       <c r="O40" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
@@ -3338,10 +3354,10 @@
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F41" t="s">
         <v>36</v>
@@ -3371,7 +3387,7 @@
         <v>18</v>
       </c>
       <c r="O41" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
@@ -3385,10 +3401,10 @@
         <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E42" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F42" t="s">
         <v>67</v>
@@ -3400,7 +3416,7 @@
         <v>99.6</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J42" t="s">
         <v>67</v>
@@ -3412,13 +3428,13 @@
         <v>19</v>
       </c>
       <c r="M42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N42" t="s">
         <v>18</v>
       </c>
       <c r="O42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
@@ -3432,13 +3448,13 @@
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E43" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G43" t="s">
         <v>18</v>
@@ -3447,10 +3463,10 @@
         <v>15.8</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K43">
         <v>88.1</v>
@@ -3459,13 +3475,64 @@
         <v>19</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N43" t="s">
         <v>18</v>
       </c>
       <c r="O43" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>180</v>
+      </c>
+      <c r="B44">
+        <v>2022</v>
+      </c>
+      <c r="C44" t="s">
+        <v>181</v>
+      </c>
+      <c r="D44" t="s">
+        <v>182</v>
+      </c>
+      <c r="E44" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>180</v>
+      </c>
+      <c r="B45">
+        <v>2022</v>
+      </c>
+      <c r="C45" t="s">
+        <v>181</v>
+      </c>
+      <c r="D45" t="s">
+        <v>183</v>
+      </c>
+      <c r="E45" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>180</v>
+      </c>
+      <c r="B46">
+        <v>2022</v>
+      </c>
+      <c r="C46" t="s">
+        <v>181</v>
+      </c>
+      <c r="D46" t="s">
+        <v>184</v>
+      </c>
+      <c r="E46" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
